--- a/Datasheets.xlsx
+++ b/Datasheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\burak\Desktop\todel\ECE445L-Lab7-8-11\deliverables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benpa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B2EF12-CCE0-454A-BFBB-D818D309FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977CCD0-05BC-4427-80EC-AF01AB37AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="5715" windowWidth="28095" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Part Name</t>
   </si>
@@ -34,16 +34,42 @@
   </si>
   <si>
     <t>Datasheet link</t>
+  </si>
+  <si>
+    <t>MPR121QR2</t>
+  </si>
+  <si>
+    <t>MPU-9250</t>
+  </si>
+  <si>
+    <t>https://invensense.tdk.com/wp-content/uploads/2015/02/PS-MPU-9250A-01-v1.1.pdf</t>
+  </si>
+  <si>
+    <t>https://cdn-shop.adafruit.com/datasheets/MPR121.pdf</t>
+  </si>
+  <si>
+    <t>Cap Sensor</t>
+  </si>
+  <si>
+    <t>IMU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,13 +92,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -351,11 +380,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="85.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -369,7 +399,33 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{C8F15EA6-AEB3-48BB-9975-3FD5B9EA3817}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{F21D1A0F-20D6-4891-A2AB-66C3CD8533B7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>